--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N7_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,23 +480,55 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
+        <v>7.87082549008093</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.817487837821458</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.542440928948966</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.884971639595996</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>W0029F0002T0006Z000C1N7.png</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
         <v>4.785943632182998</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>5.047544558629466</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="E3" t="n">
+        <v>1.542440928948966</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.884971639595996</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>T7604</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.87082549008093</v>
+        <v>1.279009142138151</v>
       </c>
       <c r="D2" t="n">
-        <v>8.817487837821458</v>
+        <v>1.432841773645987</v>
       </c>
       <c r="E2" t="n">
-        <v>1.542440928948966</v>
+        <v>0.2506466509542071</v>
       </c>
       <c r="F2" t="n">
-        <v>1.884971639595996</v>
+        <v>0.3063078914343494</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.785943632182998</v>
+        <v>0.7777158402297372</v>
       </c>
       <c r="D3" t="n">
-        <v>5.047544558629466</v>
+        <v>0.8202259907772883</v>
       </c>
       <c r="E3" t="n">
-        <v>1.542440928948966</v>
+        <v>0.2506466509542071</v>
       </c>
       <c r="F3" t="n">
-        <v>1.884971639595996</v>
+        <v>0.3063078914343494</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
